--- a/results/overall_results.xlsx
+++ b/results/overall_results.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F188534-9C7F-4683-8B77-E1610DC18978}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718350B4-A191-4A53-A9D3-D0723E8052A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="climate_change_1-step_vs_5-step" sheetId="15" r:id="rId1"/>
     <sheet name="climate_change_N_vs_H" sheetId="19" r:id="rId2"/>
-    <sheet name="blend" sheetId="25" r:id="rId3"/>
-    <sheet name="economics_1-step_vs_5-step" sheetId="17" r:id="rId4"/>
-    <sheet name="economics_N_vs_H" sheetId="20" r:id="rId5"/>
-    <sheet name="economics_blend" sheetId="26" r:id="rId6"/>
+    <sheet name="climate_change_blend" sheetId="25" r:id="rId3"/>
+    <sheet name="climate_change_phenol" sheetId="28" r:id="rId4"/>
+    <sheet name="economics_1-step_vs_5-step" sheetId="17" r:id="rId5"/>
+    <sheet name="economics_N_vs_H" sheetId="20" r:id="rId6"/>
+    <sheet name="economics_blend" sheetId="26" r:id="rId7"/>
+    <sheet name="economics_phenol" sheetId="27" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="23">
   <si>
     <t>Electricity</t>
   </si>
@@ -142,6 +144,21 @@
   <si>
     <t>STDEV</t>
   </si>
+  <si>
+    <t>Benzene</t>
+  </si>
+  <si>
+    <t>Nitrous oxide</t>
+  </si>
+  <si>
+    <t>Hydrogen peroxide</t>
+  </si>
+  <si>
+    <t>BAU</t>
+  </si>
+  <si>
+    <t>Cumene oxidation</t>
+  </si>
 </sst>
 </file>
 
@@ -183,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -219,11 +236,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -248,6 +276,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1887,6 +1921,642 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9867C95A-70AC-4F39-A762-7D8BB1440971}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4">
+        <v>4.5978906548683103</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <f>SUM(C2:J2)</f>
+        <v>4.5978906548683103</v>
+      </c>
+      <c r="L2" s="4">
+        <f>K2-2*O2</f>
+        <v>2.5242722757532103</v>
+      </c>
+      <c r="M2" s="4">
+        <f>K2+2*O2</f>
+        <v>6.6715090339834102</v>
+      </c>
+      <c r="N2" s="11">
+        <v>4.4701917929958501</v>
+      </c>
+      <c r="O2" s="4">
+        <v>1.03680918955755</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <f>A2+1</f>
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.9204799638853829</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1.3409125084288549</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.9123279562770259</v>
+      </c>
+      <c r="H3" s="4">
+        <v>3.6747694078763111E-4</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.13649996732866221</v>
+      </c>
+      <c r="K3" s="4">
+        <f>SUM(C3:J3)</f>
+        <v>4.3105878728607134</v>
+      </c>
+      <c r="L3" s="4">
+        <f>K3-2*O3</f>
+        <v>3.5051375728874881</v>
+      </c>
+      <c r="M3" s="4">
+        <f>K3+2*O3</f>
+        <v>5.1160381728339388</v>
+      </c>
+      <c r="N3" s="11">
+        <v>3.9311716518779778</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0.4027251499866128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <f>A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2.1376784824322268</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.61584237442569334</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.49408687530746859</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.8569584305448211E-3</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.153453095262118E-4</v>
+      </c>
+      <c r="K4" s="4">
+        <f>SUM(C4:J4)</f>
+        <v>3.2495800359054599</v>
+      </c>
+      <c r="L4" s="4">
+        <f>K4-2*O4</f>
+        <v>2.5067442353790739</v>
+      </c>
+      <c r="M4" s="4">
+        <f>K4+2*O4</f>
+        <v>3.9924158364318458</v>
+      </c>
+      <c r="N4" s="4">
+        <v>2.8584819043817089</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0.37141790026319305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <f>A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <f>C3</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <f>D3</f>
+        <v>1.9204799638853829</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.33392653530063571</v>
+      </c>
+      <c r="F5" s="4">
+        <f>F3</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <f>G3</f>
+        <v>0.9123279562770259</v>
+      </c>
+      <c r="H5" s="4">
+        <f>H3</f>
+        <v>3.6747694078763111E-4</v>
+      </c>
+      <c r="I5" s="4">
+        <f>I3</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <f>J3</f>
+        <v>0.13649996732866221</v>
+      </c>
+      <c r="K5" s="4">
+        <f>SUM(C5:J5)</f>
+        <v>3.3036018997324943</v>
+      </c>
+      <c r="L5" s="4">
+        <f>K5-2*O5</f>
+        <v>2.5465701836675851</v>
+      </c>
+      <c r="M5" s="4">
+        <f>K5+2*O5</f>
+        <v>4.0606336157974035</v>
+      </c>
+      <c r="N5" s="11">
+        <v>2.7651672342330831</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0.37851585803245452</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <f>A5+1</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <f>D4</f>
+        <v>2.1376784824322268</v>
+      </c>
+      <c r="E6" s="4">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.23576447452953811</v>
+      </c>
+      <c r="G6" s="4">
+        <f>G4</f>
+        <v>0.49408687530746859</v>
+      </c>
+      <c r="H6" s="4">
+        <f>H4</f>
+        <v>1.8569584305448211E-3</v>
+      </c>
+      <c r="I6" s="4">
+        <f>I4</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <f>J4</f>
+        <v>1.153453095262118E-4</v>
+      </c>
+      <c r="K6" s="4">
+        <f>SUM(C6:J6)</f>
+        <v>2.8695021360093045</v>
+      </c>
+      <c r="L6" s="4">
+        <f>K6-2*O6</f>
+        <v>2.1315763499477294</v>
+      </c>
+      <c r="M6" s="4">
+        <f>K6+2*O6</f>
+        <v>3.6074279220708796</v>
+      </c>
+      <c r="N6" s="11">
+        <v>2.4855967032186759</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0.36896289303078755</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L4:M4">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:M4">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:M2">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:M2">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:M3">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:M3">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L5:M5">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:M5">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:M6">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:M6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4124028-3522-4FAA-99F9-57399465E007}">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2255,7 +2925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0522733B-5606-4623-ABA0-C76C38F9D7AD}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2679,7 +3349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D368BAE3-24F9-4571-9515-7801E3082493}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2746,35 +3416,35 @@
         <v>10</v>
       </c>
       <c r="C2" s="4">
-        <f>economics_N_vs_H!C2*blend!$D$2+economics_N_vs_H!C4*blend!$D$4</f>
+        <f>economics_N_vs_H!C2*climate_change_blend!$D$2+economics_N_vs_H!C4*climate_change_blend!$D$4</f>
         <v>0.97421501029882962</v>
       </c>
       <c r="D2" s="4">
-        <f>economics_N_vs_H!D2*blend!$D$2+economics_N_vs_H!D4*blend!$D$4</f>
+        <f>economics_N_vs_H!D2*climate_change_blend!$D$2+economics_N_vs_H!D4*climate_change_blend!$D$4</f>
         <v>0</v>
       </c>
       <c r="E2" s="4">
-        <f>economics_N_vs_H!E2*blend!$D$2+economics_N_vs_H!E4*blend!$D$4</f>
+        <f>economics_N_vs_H!E2*climate_change_blend!$D$2+economics_N_vs_H!E4*climate_change_blend!$D$4</f>
         <v>0</v>
       </c>
       <c r="F2" s="4">
-        <f>economics_N_vs_H!F2*blend!$D$2+economics_N_vs_H!F4*blend!$D$4</f>
+        <f>economics_N_vs_H!F2*climate_change_blend!$D$2+economics_N_vs_H!F4*climate_change_blend!$D$4</f>
         <v>4.7000672476377415E-3</v>
       </c>
       <c r="G2" s="4">
-        <f>economics_N_vs_H!G2*blend!$D$2+economics_N_vs_H!G4*blend!$D$4</f>
+        <f>economics_N_vs_H!G2*climate_change_blend!$D$2+economics_N_vs_H!G4*climate_change_blend!$D$4</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f>economics_N_vs_H!H2*blend!$D$2+economics_N_vs_H!H4*blend!$D$4</f>
+        <f>economics_N_vs_H!H2*climate_change_blend!$D$2+economics_N_vs_H!H4*climate_change_blend!$D$4</f>
         <v>2.3076491450649021E-3</v>
       </c>
       <c r="I2" s="4">
-        <f>economics_N_vs_H!I2*blend!$D$2+economics_N_vs_H!I4*blend!$D$4</f>
+        <f>economics_N_vs_H!I2*climate_change_blend!$D$2+economics_N_vs_H!I4*climate_change_blend!$D$4</f>
         <v>3.2696429096004974E-2</v>
       </c>
       <c r="J2" s="4">
-        <f>economics_N_vs_H!J2*blend!$D$2+economics_N_vs_H!J4*blend!$D$4</f>
+        <f>economics_N_vs_H!J2*climate_change_blend!$D$2+economics_N_vs_H!J4*climate_change_blend!$D$4</f>
         <v>0</v>
       </c>
       <c r="K2" s="4">
@@ -2782,15 +3452,15 @@
         <v>1.0139191557875371</v>
       </c>
       <c r="L2" s="4">
-        <f>economics_N_vs_H!L2*blend!$D$2+economics_N_vs_H!L4*blend!$D$4</f>
+        <f>economics_N_vs_H!L2*climate_change_blend!$D$2+economics_N_vs_H!L4*climate_change_blend!$D$4</f>
         <v>0.79858744852640262</v>
       </c>
       <c r="M2" s="4">
-        <f>economics_N_vs_H!M2*blend!$D$2+economics_N_vs_H!M4*blend!$D$4</f>
+        <f>economics_N_vs_H!M2*climate_change_blend!$D$2+economics_N_vs_H!M4*climate_change_blend!$D$4</f>
         <v>1.2504747342536564</v>
       </c>
       <c r="N2" s="4">
-        <f>economics_N_vs_H!N2*blend!I2+economics_N_vs_H!N4*blend!I4</f>
+        <f>economics_N_vs_H!N2*climate_change_blend!I2+economics_N_vs_H!N4*climate_change_blend!I4</f>
         <v>0.79623483688153573</v>
       </c>
     </row>
@@ -2939,4 +3609,489 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CEF6791-F612-4B05-9F29-C7FAE3DBF4AF}">
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <f>SUM(C2:J2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M2" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="N2" s="11">
+        <f>K2*596.2/550.8*596.2/550.8*596.2/550.8</f>
+        <v>1.5218623269028277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <f>A2+1</f>
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.66279646911249523</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.30214844969846022</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>7.8184181448916604E-2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>4.9972870800841899E-4</v>
+      </c>
+      <c r="I3" s="4">
+        <v>4.7294145585762677E-2</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <f>SUM(C3:J3)</f>
+        <v>1.0909229745536433</v>
+      </c>
+      <c r="L3" s="4">
+        <v>1.0680000000000001</v>
+      </c>
+      <c r="M3" s="4">
+        <v>1.2070000000000001</v>
+      </c>
+      <c r="N3" s="11">
+        <v>1.167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <f>A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.73775037421411871</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.78507417812944269</v>
+      </c>
+      <c r="G4" s="4">
+        <v>4.2341987290915609E-2</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2.525261666604656E-3</v>
+      </c>
+      <c r="I4" s="4">
+        <v>6.5735640553670732E-2</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <f>SUM(C4:J4)</f>
+        <v>1.6334274418547525</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1.623</v>
+      </c>
+      <c r="M4" s="4">
+        <v>1.7390000000000001</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1.649</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <f>A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <f>D3</f>
+        <v>0.66279646911249523</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.55029119035481544</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" ref="G5:J6" si="0">G3</f>
+        <v>7.8184181448916604E-2</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.9972870800841899E-4</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.7294145585762677E-2</v>
+      </c>
+      <c r="J5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <f>SUM(C5:J5)</f>
+        <v>1.3390657152099985</v>
+      </c>
+      <c r="L5" s="4">
+        <v>1.115</v>
+      </c>
+      <c r="M5" s="4">
+        <v>1.4850000000000001</v>
+      </c>
+      <c r="N5" s="11">
+        <v>1.1679999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <f>A5+1</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <f>D4</f>
+        <v>0.73775037421411871</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.92272441962359164</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>4.2341987290915609E-2</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="0"/>
+        <v>2.525261666604656E-3</v>
+      </c>
+      <c r="I6" s="4">
+        <f t="shared" si="0"/>
+        <v>6.5735640553670732E-2</v>
+      </c>
+      <c r="J6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <f>SUM(C6:J6)</f>
+        <v>1.7710776833489015</v>
+      </c>
+      <c r="L6" s="4">
+        <v>1.675</v>
+      </c>
+      <c r="M6" s="4">
+        <v>1.8049999999999999</v>
+      </c>
+      <c r="N6" s="11">
+        <v>1.6859999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:M2">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:M4">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:M6">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:M3">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:M5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/results/overall_results.xlsx
+++ b/results/overall_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718350B4-A191-4A53-A9D3-D0723E8052A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E27A07-CE36-470F-895E-0AFF97000D31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="climate_change_1-step_vs_5-step" sheetId="15" r:id="rId1"/>
@@ -650,17 +650,17 @@
       </c>
       <c r="J2" s="4">
         <f>I2-2*M2</f>
-        <v>2.1665557159683471</v>
+        <v>2.0026681598636191</v>
       </c>
       <c r="K2" s="4">
         <f>I2+2*M2</f>
-        <v>3.4758278812997996</v>
+        <v>3.6397154374045275</v>
       </c>
       <c r="L2" s="4">
         <v>2.66364887068573</v>
       </c>
       <c r="M2" s="4">
-        <v>0.32731804133286319</v>
+        <v>0.40926181938522715</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -695,17 +695,17 @@
       </c>
       <c r="J3" s="4">
         <f>I3-2*M3</f>
-        <v>2.7206382118185779</v>
+        <v>2.4654650415390873</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" ref="K3:K5" si="0">I3+2*M3</f>
-        <v>4.1601198209018477</v>
+        <v>4.4152929911813388</v>
       </c>
       <c r="L3" s="4">
         <v>2.9332129887485459</v>
       </c>
       <c r="M3" s="4">
-        <v>0.35987040227081746</v>
+        <v>0.48745698741056281</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -745,17 +745,17 @@
       </c>
       <c r="J4" s="4">
         <f>I4-2*M4</f>
-        <v>0.34840596386625788</v>
+        <v>0.24900102092135196</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="0"/>
-        <v>1.0567130099739841</v>
+        <v>1.1561179529188899</v>
       </c>
       <c r="L4" s="4">
         <v>0.21045218805686819</v>
       </c>
       <c r="M4" s="4">
-        <v>0.17707676152693153</v>
+        <v>0.22677923299938449</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -795,17 +795,17 @@
       </c>
       <c r="J5" s="4">
         <f>I5-2*M5</f>
-        <v>0.73090244021714956</v>
+        <v>0.6258290034965821</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>1.5191505124048519</v>
+        <v>1.6242239491254193</v>
       </c>
       <c r="L5" s="4">
         <v>0.25223107945362933</v>
       </c>
       <c r="M5" s="4">
-        <v>0.19706201804692555</v>
+        <v>0.24959873640720928</v>
       </c>
     </row>
   </sheetData>
@@ -1392,17 +1392,17 @@
       </c>
       <c r="L2" s="4">
         <f>K2-2*O2</f>
-        <v>2.1665557159683471</v>
+        <v>2.0026681598636191</v>
       </c>
       <c r="M2" s="4">
         <f>K2+2*O2</f>
-        <v>3.4758278812997996</v>
+        <v>3.6397154374045275</v>
       </c>
       <c r="N2" s="4">
         <v>2.66364887068573</v>
       </c>
       <c r="O2" s="4">
-        <v>0.32731804133286319</v>
+        <v>0.40926181938522715</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" x14ac:dyDescent="0.35">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="L3" s="4">
         <f>K3-2*O3</f>
-        <v>1.0881122859301826</v>
+        <v>1.0106450775826297</v>
       </c>
       <c r="M3" s="4">
         <f>K3+2*O3</f>
-        <v>1.4832546219015195</v>
+        <v>1.5607218302490724</v>
       </c>
       <c r="N3" s="4">
         <v>1.1491449273765</v>
       </c>
       <c r="O3" s="4">
-        <v>9.8785583992834256E-2</v>
+        <v>0.13751918816661066</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" x14ac:dyDescent="0.35">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="L4" s="4">
         <f>K4-2*O4</f>
-        <v>0.34840596386625788</v>
+        <v>0.24900102092135196</v>
       </c>
       <c r="M4" s="4">
         <f>K4+2*O4</f>
-        <v>1.0567130099739841</v>
+        <v>1.1561179529188899</v>
       </c>
       <c r="N4" s="4">
         <v>0.21045218805686819</v>
       </c>
       <c r="O4" s="4">
-        <v>0.17707676152693153</v>
+        <v>0.22677923299938449</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" x14ac:dyDescent="0.35">
@@ -1558,17 +1558,17 @@
       </c>
       <c r="L5" s="4">
         <f>K5-2*O5</f>
-        <v>0.32534263909664451</v>
+        <v>0.29838309889064307</v>
       </c>
       <c r="M5" s="4">
         <f>K5+2*O5</f>
-        <v>0.65906012724085794</v>
+        <v>0.68601966744685938</v>
       </c>
       <c r="N5" s="4">
         <v>0.37067895766329961</v>
       </c>
       <c r="O5" s="4">
-        <v>8.3429372036053343E-2</v>
+        <v>9.6909142139054077E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2020,17 +2020,17 @@
       </c>
       <c r="L2" s="4">
         <f>K2-2*O2</f>
-        <v>2.5242722757532103</v>
+        <v>2.5535251294712804</v>
       </c>
       <c r="M2" s="4">
         <f>K2+2*O2</f>
-        <v>6.6715090339834102</v>
+        <v>6.6422561802653401</v>
       </c>
       <c r="N2" s="11">
         <v>4.4701917929958501</v>
       </c>
       <c r="O2" s="4">
-        <v>1.03680918955755</v>
+        <v>1.0221827626985149</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" x14ac:dyDescent="0.35">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="L3" s="4">
         <f>K3-2*O3</f>
-        <v>3.5051375728874881</v>
+        <v>3.3139311707373849</v>
       </c>
       <c r="M3" s="4">
         <f>K3+2*O3</f>
-        <v>5.1160381728339388</v>
+        <v>5.3072445749840425</v>
       </c>
       <c r="N3" s="11">
         <v>3.9311716518779778</v>
       </c>
       <c r="O3" s="4">
-        <v>0.4027251499866128</v>
+        <v>0.49832835106166434</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" x14ac:dyDescent="0.35">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="L4" s="4">
         <f>K4-2*O4</f>
-        <v>2.5067442353790739</v>
+        <v>2.3295545342349353</v>
       </c>
       <c r="M4" s="4">
         <f>K4+2*O4</f>
-        <v>3.9924158364318458</v>
+        <v>4.1696055375759844</v>
       </c>
       <c r="N4" s="4">
         <v>2.8584819043817089</v>
       </c>
       <c r="O4" s="4">
-        <v>0.37141790026319305</v>
+        <v>0.46001275083526216</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" x14ac:dyDescent="0.35">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L5" s="4">
         <f>K5-2*O5</f>
-        <v>2.5465701836675851</v>
+        <v>2.4029213493690715</v>
       </c>
       <c r="M5" s="4">
         <f>K5+2*O5</f>
-        <v>4.0606336157974035</v>
+        <v>4.2042824500959171</v>
       </c>
       <c r="N5" s="11">
         <v>2.7651672342330831</v>
       </c>
       <c r="O5" s="4">
-        <v>0.37851585803245452</v>
+        <v>0.45034027518171138</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="18" x14ac:dyDescent="0.35">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="L6" s="4">
         <f>K6-2*O6</f>
-        <v>2.1315763499477294</v>
+        <v>1.9519486846748575</v>
       </c>
       <c r="M6" s="4">
         <f>K6+2*O6</f>
-        <v>3.6074279220708796</v>
+        <v>3.7870555873437515</v>
       </c>
       <c r="N6" s="11">
         <v>2.4855967032186759</v>
       </c>
       <c r="O6" s="4">
-        <v>0.36896289303078755</v>
+        <v>0.45877672566722355</v>
       </c>
     </row>
   </sheetData>

--- a/results/overall_results.xlsx
+++ b/results/overall_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E27A07-CE36-470F-895E-0AFF97000D31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402F4CE9-75F6-470A-B584-EF0C5868F48D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="climate_change_1-step_vs_5-step" sheetId="15" r:id="rId1"/>

--- a/results/overall_results.xlsx
+++ b/results/overall_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402F4CE9-75F6-470A-B584-EF0C5868F48D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85A0901-8DC1-49E7-8C46-6EAABAD1D33B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,8 +164,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -251,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -282,6 +283,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -644,7 +651,7 @@
       <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="12">
         <f>SUM(C2:H2)</f>
         <v>2.8211917986340733</v>
       </c>
@@ -689,7 +696,7 @@
       <c r="H3" s="4">
         <v>2.530295351022005E-8</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="12">
         <f>SUM(C3:H3)</f>
         <v>3.4403790163602128</v>
       </c>
@@ -739,7 +746,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="12">
         <f>SUM(C4:H4)</f>
         <v>0.70255948692012093</v>
       </c>
@@ -789,7 +796,7 @@
         <f t="shared" si="2"/>
         <v>2.530295351022005E-8</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="12">
         <f>SUM(C5:H5)</f>
         <v>1.1250264763110007</v>
       </c>
@@ -1386,7 +1393,7 @@
       <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="12">
         <f>SUM(C2:J2)</f>
         <v>2.8211917986340733</v>
       </c>
@@ -1437,7 +1444,7 @@
       <c r="J3" s="4">
         <v>8.1327667296859252E-2</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="12">
         <f>SUM(C3:J3)</f>
         <v>1.285683453915851</v>
       </c>
@@ -1495,7 +1502,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="12">
         <f>SUM(C4:J4)</f>
         <v>0.70255948692012093</v>
       </c>
@@ -1507,7 +1514,7 @@
         <f>K4+2*O4</f>
         <v>1.1561179529188899</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="12">
         <v>0.21045218805686819</v>
       </c>
       <c r="O4" s="4">
@@ -1552,7 +1559,7 @@
         <f t="shared" si="2"/>
         <v>8.1327667296859252E-2</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="12">
         <f>SUM(C5:J5)</f>
         <v>0.49220138316875123</v>
       </c>
@@ -1564,7 +1571,7 @@
         <f>K5+2*O5</f>
         <v>0.68601966744685938</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="12">
         <v>0.37067895766329961</v>
       </c>
       <c r="O5" s="4">
@@ -2014,7 +2021,7 @@
       <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="12">
         <f>SUM(C2:J2)</f>
         <v>4.5978906548683103</v>
       </c>
@@ -2065,7 +2072,7 @@
       <c r="J3" s="4">
         <v>0.13649996732866221</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="12">
         <f>SUM(C3:J3)</f>
         <v>4.3105878728607134</v>
       </c>
@@ -2077,7 +2084,7 @@
         <f>K3+2*O3</f>
         <v>5.3072445749840425</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="13">
         <v>3.9311716518779778</v>
       </c>
       <c r="O3" s="4">
@@ -2116,7 +2123,7 @@
       <c r="J4" s="4">
         <v>1.153453095262118E-4</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="12">
         <f>SUM(C4:J4)</f>
         <v>3.2495800359054599</v>
       </c>
@@ -2128,7 +2135,7 @@
         <f>K4+2*O4</f>
         <v>4.1696055375759844</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="12">
         <v>2.8584819043817089</v>
       </c>
       <c r="O4" s="4">
@@ -2174,7 +2181,7 @@
         <f>J3</f>
         <v>0.13649996732866221</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="12">
         <f>SUM(C5:J5)</f>
         <v>3.3036018997324943</v>
       </c>
@@ -2186,7 +2193,7 @@
         <f>K5+2*O5</f>
         <v>4.2042824500959171</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="13">
         <v>2.7651672342330831</v>
       </c>
       <c r="O5" s="4">
@@ -2232,7 +2239,7 @@
         <f>J4</f>
         <v>1.153453095262118E-4</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="12">
         <f>SUM(C6:J6)</f>
         <v>2.8695021360093045</v>
       </c>
@@ -2244,7 +2251,7 @@
         <f>K6+2*O6</f>
         <v>3.7870555873437515</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="13">
         <v>2.4855967032186759</v>
       </c>
       <c r="O6" s="4">
@@ -2633,7 +2640,7 @@
       <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="12">
         <f>SUM(C2:H2)</f>
         <v>0.6356470646863307</v>
       </c>
@@ -2673,7 +2680,7 @@
       <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="12">
         <f>SUM(C3:H3)</f>
         <v>0.85047341433644497</v>
       </c>
@@ -2718,7 +2725,7 @@
         <f>H2</f>
         <v>0</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="12">
         <f>SUM(C4:H4)</f>
         <v>1.1576792143758208</v>
       </c>
@@ -2762,7 +2769,7 @@
       <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="12">
         <f>SUM(C5:H5)</f>
         <v>1.4209775348900924</v>
       </c>
@@ -3015,7 +3022,7 @@
       <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="12">
         <f>SUM(C2:J2)</f>
         <v>0.6356470646863307</v>
       </c>
@@ -3061,7 +3068,7 @@
       <c r="J3" s="4">
         <v>0</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="12">
         <f>SUM(C3:J3)</f>
         <v>1.6389388786333619</v>
       </c>
@@ -3109,7 +3116,7 @@
       <c r="J4" s="4">
         <v>0</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="12">
         <f>SUM(C4:J4)</f>
         <v>1.1576792143758208</v>
       </c>
@@ -3162,7 +3169,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="12">
         <f>SUM(C5:J5)</f>
         <v>1.9263006830625418</v>
       </c>
@@ -3447,7 +3454,7 @@
         <f>economics_N_vs_H!J2*climate_change_blend!$D$2+economics_N_vs_H!J4*climate_change_blend!$D$4</f>
         <v>0</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="12">
         <f>SUM(C2:J2)</f>
         <v>1.0139191557875371</v>
       </c>
@@ -3496,7 +3503,7 @@
       <c r="J3" s="4">
         <v>0</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="12">
         <f>SUM(C3:J3)</f>
         <v>1.6389388786333619</v>
       </c>
@@ -3702,7 +3709,7 @@
       <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="12">
         <f>SUM(C2:J2)</f>
         <v>1.2</v>
       </c>
@@ -3749,7 +3756,7 @@
       <c r="J3" s="4">
         <v>0</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="12">
         <f>SUM(C3:J3)</f>
         <v>1.0909229745536433</v>
       </c>
@@ -3795,7 +3802,7 @@
       <c r="J4" s="4">
         <v>0</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="12">
         <f>SUM(C4:J4)</f>
         <v>1.6334274418547525</v>
       </c>
@@ -3846,7 +3853,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="12">
         <f>SUM(C5:J5)</f>
         <v>1.3390657152099985</v>
       </c>
@@ -3897,7 +3904,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="12">
         <f>SUM(C6:J6)</f>
         <v>1.7710776833489015</v>
       </c>

--- a/results/overall_results.xlsx
+++ b/results/overall_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85A0901-8DC1-49E7-8C46-6EAABAD1D33B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030BCF88-B82E-43E6-8A8A-A9578813D459}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2640,7 +2640,7 @@
       <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="4">
         <f>SUM(C2:H2)</f>
         <v>0.6356470646863307</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>0.68600000000000005</v>
       </c>
       <c r="L2" s="4">
-        <v>0.79500000000000004</v>
+        <v>0.45700000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2680,7 +2680,7 @@
       <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="4">
         <f>SUM(C3:H3)</f>
         <v>0.85047341433644497</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>0.90500000000000003</v>
       </c>
       <c r="L3" s="4">
-        <v>1.0249999999999999</v>
+        <v>0.65500000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2725,7 +2725,7 @@
         <f>H2</f>
         <v>0</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="4">
         <f>SUM(C4:H4)</f>
         <v>1.1576792143758208</v>
       </c>
@@ -2769,7 +2769,7 @@
       <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="4">
         <f>SUM(C5:H5)</f>
         <v>1.4209775348900924</v>
       </c>
@@ -3022,7 +3022,7 @@
       <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="4">
         <f>SUM(C2:J2)</f>
         <v>0.6356470646863307</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>0.68600000000000005</v>
       </c>
       <c r="N2" s="4">
-        <v>0.79500000000000004</v>
+        <v>0.45700000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -3068,7 +3068,7 @@
       <c r="J3" s="4">
         <v>0</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="4">
         <f>SUM(C3:J3)</f>
         <v>1.6389388786333619</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>1.726</v>
       </c>
       <c r="N3" s="4">
-        <v>1.6715562972717923</v>
+        <v>1.6024744255877656</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -3116,7 +3116,7 @@
       <c r="J4" s="4">
         <v>0</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="4">
         <f>SUM(C4:J4)</f>
         <v>1.1576792143758208</v>
       </c>
@@ -3169,7 +3169,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="4">
         <f>SUM(C5:J5)</f>
         <v>1.9263006830625418</v>
       </c>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="N2" s="4">
         <f>economics_N_vs_H!N2*climate_change_blend!I2+economics_N_vs_H!N4*climate_change_blend!I4</f>
-        <v>0.79623483688153573</v>
+        <v>0.6669222698610906</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -3514,7 +3514,7 @@
         <v>1.726</v>
       </c>
       <c r="N3" s="4">
-        <v>1.6715562972717923</v>
+        <v>1.6024744255877656</v>
       </c>
     </row>
   </sheetData>
@@ -3709,7 +3709,7 @@
       <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="4">
         <f>SUM(C2:J2)</f>
         <v>1.2</v>
       </c>
@@ -3720,8 +3720,8 @@
         <v>1.7</v>
       </c>
       <c r="N2" s="11">
-        <f>K2*596.2/550.8*596.2/550.8*596.2/550.8</f>
-        <v>1.5218623269028277</v>
+        <f>K2*596.2/550.8*596.2/550.8*596.2/550.8/(1+0.02)^30</f>
+        <v>0.84017588771828156</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -3756,7 +3756,7 @@
       <c r="J3" s="4">
         <v>0</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="4">
         <f>SUM(C3:J3)</f>
         <v>1.0909229745536433</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>1.2070000000000001</v>
       </c>
       <c r="N3" s="11">
-        <v>1.167</v>
+        <v>1.0060048861411819</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -3802,7 +3802,7 @@
       <c r="J4" s="4">
         <v>0</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="4">
         <f>SUM(C4:J4)</f>
         <v>1.6334274418547525</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>1.7390000000000001</v>
       </c>
       <c r="N4" s="1">
-        <v>1.649</v>
+        <v>1.6160000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
@@ -3853,7 +3853,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="4">
         <f>SUM(C5:J5)</f>
         <v>1.3390657152099985</v>
       </c>
@@ -3904,7 +3904,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="4">
         <f>SUM(C6:J6)</f>
         <v>1.7710776833489015</v>
       </c>

--- a/results/overall_results.xlsx
+++ b/results/overall_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030BCF88-B82E-43E6-8A8A-A9578813D459}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5B0183-BD3B-46A2-9A9F-4EC80A6BAC42}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="climate_change_1-step_vs_5-step" sheetId="15" r:id="rId1"/>
@@ -663,7 +663,7 @@
         <f>I2+2*M2</f>
         <v>3.6397154374045275</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="12">
         <v>2.66364887068573</v>
       </c>
       <c r="M2" s="4">
@@ -708,7 +708,7 @@
         <f t="shared" ref="K3:K5" si="0">I3+2*M3</f>
         <v>4.4152929911813388</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="12">
         <v>2.9332129887485459</v>
       </c>
       <c r="M3" s="4">
@@ -758,7 +758,7 @@
         <f t="shared" si="0"/>
         <v>1.1561179529188899</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="12">
         <v>0.21045218805686819</v>
       </c>
       <c r="M4" s="4">
@@ -808,7 +808,7 @@
         <f t="shared" si="0"/>
         <v>1.6242239491254193</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="12">
         <v>0.25223107945362933</v>
       </c>
       <c r="M5" s="4">
@@ -852,7 +852,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2 K2">
+  <conditionalFormatting sqref="K2 I2">
     <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
@@ -972,7 +972,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3 K3">
+  <conditionalFormatting sqref="K3 I3">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -1092,7 +1092,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4 K4">
+  <conditionalFormatting sqref="K4 I4">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -1212,7 +1212,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5 K5">
+  <conditionalFormatting sqref="K5 I5">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2640,7 +2640,7 @@
       <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="12">
         <f>SUM(C2:H2)</f>
         <v>0.6356470646863307</v>
       </c>
@@ -2680,7 +2680,7 @@
       <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="12">
         <f>SUM(C3:H3)</f>
         <v>0.85047341433644497</v>
       </c>
@@ -2725,7 +2725,7 @@
         <f>H2</f>
         <v>0</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="12">
         <f>SUM(C4:H4)</f>
         <v>1.1576792143758208</v>
       </c>
@@ -2769,7 +2769,7 @@
       <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="12">
         <f>SUM(C5:H5)</f>
         <v>1.4209775348900924</v>
       </c>
